--- a/public/formsExcelTemplates/Epicrisis.xlsx
+++ b/public/formsExcelTemplates/Epicrisis.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Datos básicos</t>
   </si>
   <si>
-    <t xml:space="preserve">Nombre completo del paciente</t>
+    <t xml:space="preserve">Nombre completo</t>
   </si>
   <si>
     <t xml:space="preserve">Número de historia clínica</t>
